--- a/data/GreatLink/GreatLink US Income and Growth Fund (Dis).xlsx
+++ b/data/GreatLink/GreatLink US Income and Growth Fund (Dis).xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid476276"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid315280"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="767">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,15 +26,120 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>03/12/2025</t>
+  </si>
+  <si>
+    <t>1.008</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>02/12/2025</t>
+  </si>
+  <si>
+    <t>1.012</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>1.011</t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
+    <t>27/11/2025</t>
+  </si>
+  <si>
+    <t>1.006</t>
+  </si>
+  <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>0.998</t>
+  </si>
+  <si>
+    <t>24/11/2025</t>
+  </si>
+  <si>
+    <t>0.993</t>
+  </si>
+  <si>
+    <t>21/11/2025</t>
+  </si>
+  <si>
+    <t>0.985</t>
+  </si>
+  <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>1.003</t>
+  </si>
+  <si>
+    <t>19/11/2025</t>
+  </si>
+  <si>
+    <t>0.995</t>
+  </si>
+  <si>
+    <t>18/11/2025</t>
+  </si>
+  <si>
+    <t>0.996</t>
+  </si>
+  <si>
+    <t>17/11/2025</t>
+  </si>
+  <si>
+    <t>1.005</t>
+  </si>
+  <si>
+    <t>14/11/2025</t>
+  </si>
+  <si>
+    <t>13/11/2025</t>
+  </si>
+  <si>
+    <t>1.015</t>
+  </si>
+  <si>
+    <t>12/11/2025</t>
+  </si>
+  <si>
+    <t>1.021</t>
+  </si>
+  <si>
+    <t>11/11/2025</t>
+  </si>
+  <si>
+    <t>1.019</t>
+  </si>
+  <si>
+    <t>10/11/2025</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
+    <t>05/11/2025</t>
+  </si>
+  <si>
     <t>04/11/2025</t>
   </si>
   <si>
     <t>1.016</t>
   </si>
   <si>
-    <t>SGD</t>
-  </si>
-  <si>
     <t>03/11/2025</t>
   </si>
   <si>
@@ -77,18 +182,12 @@
     <t>22/10/2025</t>
   </si>
   <si>
-    <t>1.011</t>
-  </si>
-  <si>
     <t>21/10/2025</t>
   </si>
   <si>
     <t>17/10/2025</t>
   </si>
   <si>
-    <t>1.005</t>
-  </si>
-  <si>
     <t>16/10/2025</t>
   </si>
   <si>
@@ -143,15 +242,9 @@
     <t>29/09/2025</t>
   </si>
   <si>
-    <t>1.012</t>
-  </si>
-  <si>
     <t>26/09/2025</t>
   </si>
   <si>
-    <t>1.008</t>
-  </si>
-  <si>
     <t>25/09/2025</t>
   </si>
   <si>
@@ -164,9 +257,6 @@
     <t>22/09/2025</t>
   </si>
   <si>
-    <t>1.015</t>
-  </si>
-  <si>
     <t>19/09/2025</t>
   </si>
   <si>
@@ -221,9 +311,6 @@
     <t>02/09/2025</t>
   </si>
   <si>
-    <t>0.998</t>
-  </si>
-  <si>
     <t>01/09/2025</t>
   </si>
   <si>
@@ -275,9 +362,6 @@
     <t>15/08/2025</t>
   </si>
   <si>
-    <t>1.006</t>
-  </si>
-  <si>
     <t>14/08/2025</t>
   </si>
   <si>
@@ -296,9 +380,6 @@
     <t>07/08/2025</t>
   </si>
   <si>
-    <t>1.003</t>
-  </si>
-  <si>
     <t>06/08/2025</t>
   </si>
   <si>
@@ -341,9 +422,6 @@
     <t>22/07/2025</t>
   </si>
   <si>
-    <t>0.996</t>
-  </si>
-  <si>
     <t>21/07/2025</t>
   </si>
   <si>
@@ -353,9 +431,6 @@
     <t>17/07/2025</t>
   </si>
   <si>
-    <t>0.995</t>
-  </si>
-  <si>
     <t>16/07/2025</t>
   </si>
   <si>
@@ -389,9 +464,6 @@
     <t>02/07/2025</t>
   </si>
   <si>
-    <t>0.993</t>
-  </si>
-  <si>
     <t>01/07/2025</t>
   </si>
   <si>
@@ -410,9 +482,6 @@
     <t>25/06/2025</t>
   </si>
   <si>
-    <t>0.985</t>
-  </si>
-  <si>
     <t>24/06/2025</t>
   </si>
   <si>
@@ -941,9 +1010,6 @@
     <t>11/12/2024</t>
   </si>
   <si>
-    <t>1.021</t>
-  </si>
-  <si>
     <t>10/12/2024</t>
   </si>
   <si>
@@ -960,9 +1026,6 @@
   </si>
   <si>
     <t>04/12/2024</t>
-  </si>
-  <si>
-    <t>1.019</t>
   </si>
   <si>
     <t>03/12/2024</t>
@@ -2649,7 +2712,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -2657,10 +2720,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
         <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -2671,7 +2734,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -2679,10 +2742,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -2690,10 +2753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -2701,10 +2764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -2712,10 +2775,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -2723,10 +2786,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -2734,10 +2797,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -2745,10 +2808,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -2756,10 +2819,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -2767,10 +2830,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -2778,10 +2841,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -2789,10 +2852,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -2800,10 +2863,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -2811,10 +2874,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -2822,10 +2885,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -2833,10 +2896,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -2844,10 +2907,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -2855,10 +2918,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -2866,10 +2929,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -2877,10 +2940,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -2888,10 +2951,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -2899,10 +2962,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -2910,10 +2973,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -2921,10 +2984,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -2932,10 +2995,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -2943,10 +3006,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -2954,10 +3017,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -2965,10 +3028,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -2976,10 +3039,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -2987,10 +3050,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -2998,10 +3061,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -3009,10 +3072,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -3020,10 +3083,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -3031,10 +3094,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -3042,10 +3105,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -3053,10 +3116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -3064,10 +3127,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -3075,10 +3138,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
@@ -3086,10 +3149,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
@@ -3097,10 +3160,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -3108,10 +3171,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -3119,10 +3182,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -3130,10 +3193,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -3141,10 +3204,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B52" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -3152,10 +3215,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="C53" t="s">
         <v>5</v>
@@ -3163,10 +3226,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -3177,7 +3240,7 @@
         <v>81</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -3185,10 +3248,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B56" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
@@ -3199,7 +3262,7 @@
         <v>84</v>
       </c>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -3210,7 +3273,7 @@
         <v>85</v>
       </c>
       <c r="B58" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -3218,10 +3281,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
@@ -3229,10 +3292,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -3240,10 +3303,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -3251,10 +3314,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B62" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -3262,10 +3325,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>90</v>
+      </c>
+      <c r="B63" t="s">
         <v>91</v>
-      </c>
-      <c r="B63" t="s">
-        <v>76</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -3276,7 +3339,7 @@
         <v>92</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -3284,10 +3347,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65" t="s">
         <v>94</v>
-      </c>
-      <c r="B65" t="s">
-        <v>68</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -3298,7 +3361,7 @@
         <v>95</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -3306,10 +3369,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B67" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
@@ -3331,7 +3394,7 @@
         <v>100</v>
       </c>
       <c r="B69" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
@@ -3342,7 +3405,7 @@
         <v>101</v>
       </c>
       <c r="B70" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
@@ -3353,7 +3416,7 @@
         <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -3364,7 +3427,7 @@
         <v>103</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C72" t="s">
         <v>5</v>
@@ -3375,7 +3438,7 @@
         <v>104</v>
       </c>
       <c r="B73" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C73" t="s">
         <v>5</v>
@@ -3383,10 +3446,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B74" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
@@ -3394,10 +3457,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B75" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
@@ -3405,10 +3468,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B76" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
@@ -3416,10 +3479,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B77" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="C77" t="s">
         <v>5</v>
@@ -3427,10 +3490,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B78" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C78" t="s">
         <v>5</v>
@@ -3438,10 +3501,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B79" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
         <v>5</v>
@@ -3449,10 +3512,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B80" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="C80" t="s">
         <v>5</v>
@@ -3460,10 +3523,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B81" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
@@ -3471,10 +3534,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B82" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C82" t="s">
         <v>5</v>
@@ -3482,10 +3545,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B83" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C83" t="s">
         <v>5</v>
@@ -3493,10 +3556,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B84" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C84" t="s">
         <v>5</v>
@@ -3504,10 +3567,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="C85" t="s">
         <v>5</v>
@@ -3515,10 +3578,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B86" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
@@ -3526,10 +3589,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B87" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C87" t="s">
         <v>5</v>
@@ -3537,10 +3600,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B88" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="C88" t="s">
         <v>5</v>
@@ -3548,10 +3611,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B89" t="s">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="C89" t="s">
         <v>5</v>
@@ -3559,10 +3622,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B90" t="s">
-        <v>124</v>
+        <v>12</v>
       </c>
       <c r="C90" t="s">
         <v>5</v>
@@ -3570,10 +3633,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B91" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C91" t="s">
         <v>5</v>
@@ -3581,10 +3644,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B92" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
@@ -3592,7 +3655,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B93" t="s">
         <v>99</v>
@@ -3603,10 +3666,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B94" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="C94" t="s">
         <v>5</v>
@@ -3614,10 +3677,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B95" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="C95" t="s">
         <v>5</v>
@@ -3625,10 +3688,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B96" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="C96" t="s">
         <v>5</v>
@@ -3639,7 +3702,7 @@
         <v>134</v>
       </c>
       <c r="B97" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="C97" t="s">
         <v>5</v>
@@ -3647,10 +3710,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B98" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="C98" t="s">
         <v>5</v>
@@ -3658,10 +3721,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B99" t="s">
-        <v>138</v>
+        <v>15</v>
       </c>
       <c r="C99" t="s">
         <v>5</v>
@@ -3669,10 +3732,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B100" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="C100" t="s">
         <v>5</v>
@@ -3680,10 +3743,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B101" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="C101" t="s">
         <v>5</v>
@@ -3691,10 +3754,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B102" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="C102" t="s">
         <v>5</v>
@@ -3702,10 +3765,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B103" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="C103" t="s">
         <v>5</v>
@@ -3713,10 +3776,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B104" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="C104" t="s">
         <v>5</v>
@@ -3724,10 +3787,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B105" t="s">
-        <v>148</v>
+        <v>15</v>
       </c>
       <c r="C105" t="s">
         <v>5</v>
@@ -3735,10 +3798,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B106" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="C106" t="s">
         <v>5</v>
@@ -3746,10 +3809,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B107" t="s">
-        <v>143</v>
+        <v>15</v>
       </c>
       <c r="C107" t="s">
         <v>5</v>
@@ -3757,10 +3820,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B108" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="C108" t="s">
         <v>5</v>
@@ -3768,10 +3831,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B109" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="C109" t="s">
         <v>5</v>
@@ -3779,10 +3842,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B110" t="s">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="C110" t="s">
         <v>5</v>
@@ -3790,10 +3853,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B111" t="s">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c r="C111" t="s">
         <v>5</v>
@@ -3801,10 +3864,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B112" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="C112" t="s">
         <v>5</v>
@@ -3812,10 +3875,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B113" t="s">
-        <v>156</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
         <v>5</v>
@@ -3823,10 +3886,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B114" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="C114" t="s">
         <v>5</v>
@@ -3834,10 +3897,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B115" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C115" t="s">
         <v>5</v>
@@ -3845,10 +3908,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B116" t="s">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="C116" t="s">
         <v>5</v>
@@ -3856,10 +3919,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B117" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C117" t="s">
         <v>5</v>
@@ -3867,10 +3930,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B118" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C118" t="s">
         <v>5</v>
@@ -3878,10 +3941,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B119" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C119" t="s">
         <v>5</v>
@@ -3889,10 +3952,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B120" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C120" t="s">
         <v>5</v>
@@ -3900,10 +3963,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B121" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C121" t="s">
         <v>5</v>
@@ -3911,10 +3974,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B122" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -3922,10 +3985,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B123" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="C123" t="s">
         <v>5</v>
@@ -3933,10 +3996,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B124" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C124" t="s">
         <v>5</v>
@@ -3944,10 +4007,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B125" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C125" t="s">
         <v>5</v>
@@ -3955,10 +4018,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B126" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C126" t="s">
         <v>5</v>
@@ -3966,10 +4029,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B127" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C127" t="s">
         <v>5</v>
@@ -3977,10 +4040,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B128" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C128" t="s">
         <v>5</v>
@@ -3988,10 +4051,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B129" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C129" t="s">
         <v>5</v>
@@ -3999,10 +4062,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B130" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C130" t="s">
         <v>5</v>
@@ -4010,10 +4073,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B131" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="C131" t="s">
         <v>5</v>
@@ -4021,10 +4084,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B132" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C132" t="s">
         <v>5</v>
@@ -4032,10 +4095,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C133" t="s">
         <v>5</v>
@@ -4043,10 +4106,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B134" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C134" t="s">
         <v>5</v>
@@ -4054,10 +4117,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B135" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C135" t="s">
         <v>5</v>
@@ -4065,10 +4128,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B136" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C136" t="s">
         <v>5</v>
@@ -4076,10 +4139,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B137" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="C137" t="s">
         <v>5</v>
@@ -4087,10 +4150,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B138" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C138" t="s">
         <v>5</v>
@@ -4098,10 +4161,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B139" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C139" t="s">
         <v>5</v>
@@ -4109,10 +4172,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B140" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C140" t="s">
         <v>5</v>
@@ -4120,10 +4183,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B141" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="C141" t="s">
         <v>5</v>
@@ -4131,10 +4194,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B142" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C142" t="s">
         <v>5</v>
@@ -4142,10 +4205,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B143" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="C143" t="s">
         <v>5</v>
@@ -4153,10 +4216,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B144" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="C144" t="s">
         <v>5</v>
@@ -4164,10 +4227,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B145" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C145" t="s">
         <v>5</v>
@@ -4175,10 +4238,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B146" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="C146" t="s">
         <v>5</v>
@@ -4186,10 +4249,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B147" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="C147" t="s">
         <v>5</v>
@@ -4197,7 +4260,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B148" t="s">
         <v>199</v>
@@ -4208,10 +4271,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="B149" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C149" t="s">
         <v>5</v>
@@ -4219,10 +4282,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B150" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="C150" t="s">
         <v>5</v>
@@ -4230,10 +4293,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B151" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C151" t="s">
         <v>5</v>
@@ -4241,10 +4304,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="B152" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C152" t="s">
         <v>5</v>
@@ -4252,10 +4315,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B153" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="C153" t="s">
         <v>5</v>
@@ -4263,10 +4326,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="B154" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C154" t="s">
         <v>5</v>
@@ -4274,10 +4337,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B155" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C155" t="s">
         <v>5</v>
@@ -4285,10 +4348,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="B156" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="C156" t="s">
         <v>5</v>
@@ -4296,10 +4359,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B157" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C157" t="s">
         <v>5</v>
@@ -4307,10 +4370,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="B158" t="s">
-        <v>156</v>
+        <v>216</v>
       </c>
       <c r="C158" t="s">
         <v>5</v>
@@ -4318,10 +4381,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="B159" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C159" t="s">
         <v>5</v>
@@ -4329,10 +4392,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="B160" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C160" t="s">
         <v>5</v>
@@ -4340,10 +4403,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="B161" t="s">
-        <v>176</v>
+        <v>222</v>
       </c>
       <c r="C161" t="s">
         <v>5</v>
@@ -4351,10 +4414,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B162" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="C162" t="s">
         <v>5</v>
@@ -4362,10 +4425,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B163" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="C163" t="s">
         <v>5</v>
@@ -4373,10 +4436,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B164" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C164" t="s">
         <v>5</v>
@@ -4384,10 +4447,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="B165" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="C165" t="s">
         <v>5</v>
@@ -4395,10 +4458,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B166" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C166" t="s">
         <v>5</v>
@@ -4406,10 +4469,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B167" t="s">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="C167" t="s">
         <v>5</v>
@@ -4417,10 +4480,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="B168" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C168" t="s">
         <v>5</v>
@@ -4428,10 +4491,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B169" t="s">
-        <v>135</v>
+        <v>222</v>
       </c>
       <c r="C169" t="s">
         <v>5</v>
@@ -4439,10 +4502,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B170" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C170" t="s">
         <v>5</v>
@@ -4450,10 +4513,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B171" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="C171" t="s">
         <v>5</v>
@@ -4461,10 +4524,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B172" t="s">
-        <v>141</v>
+        <v>241</v>
       </c>
       <c r="C172" t="s">
         <v>5</v>
@@ -4472,10 +4535,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B173" t="s">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="C173" t="s">
         <v>5</v>
@@ -4483,10 +4546,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B174" t="s">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="C174" t="s">
         <v>5</v>
@@ -4494,10 +4557,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B175" t="s">
-        <v>124</v>
+        <v>243</v>
       </c>
       <c r="C175" t="s">
         <v>5</v>
@@ -4505,10 +4568,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B176" t="s">
-        <v>108</v>
+        <v>247</v>
       </c>
       <c r="C176" t="s">
         <v>5</v>
@@ -4516,10 +4579,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B177" t="s">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="C177" t="s">
         <v>5</v>
@@ -4527,10 +4590,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B178" t="s">
-        <v>108</v>
+        <v>251</v>
       </c>
       <c r="C178" t="s">
         <v>5</v>
@@ -4538,10 +4601,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B179" t="s">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="C179" t="s">
         <v>5</v>
@@ -4549,10 +4612,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B180" t="s">
-        <v>61</v>
+        <v>254</v>
       </c>
       <c r="C180" t="s">
         <v>5</v>
@@ -4560,10 +4623,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B181" t="s">
-        <v>39</v>
+        <v>256</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -4571,10 +4634,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B182" t="s">
-        <v>28</v>
+        <v>199</v>
       </c>
       <c r="C182" t="s">
         <v>5</v>
@@ -4582,10 +4645,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B183" t="s">
-        <v>4</v>
+        <v>259</v>
       </c>
       <c r="C183" t="s">
         <v>5</v>
@@ -4593,10 +4656,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B184" t="s">
-        <v>4</v>
+        <v>261</v>
       </c>
       <c r="C184" t="s">
         <v>5</v>
@@ -4604,10 +4667,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B185" t="s">
-        <v>42</v>
+        <v>254</v>
       </c>
       <c r="C185" t="s">
         <v>5</v>
@@ -4615,10 +4678,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B186" t="s">
-        <v>44</v>
+        <v>199</v>
       </c>
       <c r="C186" t="s">
         <v>5</v>
@@ -4626,10 +4689,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
+        <v>264</v>
+      </c>
+      <c r="B187" t="s">
         <v>265</v>
-      </c>
-      <c r="B187" t="s">
-        <v>20</v>
       </c>
       <c r="C187" t="s">
         <v>5</v>
@@ -4640,7 +4703,7 @@
         <v>266</v>
       </c>
       <c r="B188" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="C188" t="s">
         <v>5</v>
@@ -4651,7 +4714,7 @@
         <v>267</v>
       </c>
       <c r="B189" t="s">
-        <v>49</v>
+        <v>261</v>
       </c>
       <c r="C189" t="s">
         <v>5</v>
@@ -4662,7 +4725,7 @@
         <v>268</v>
       </c>
       <c r="B190" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="C190" t="s">
         <v>5</v>
@@ -4673,7 +4736,7 @@
         <v>269</v>
       </c>
       <c r="B191" t="s">
-        <v>18</v>
+        <v>270</v>
       </c>
       <c r="C191" t="s">
         <v>5</v>
@@ -4681,10 +4744,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B192" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="C192" t="s">
         <v>5</v>
@@ -4692,10 +4755,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B193" t="s">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="C193" t="s">
         <v>5</v>
@@ -4703,10 +4766,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B194" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="C194" t="s">
         <v>5</v>
@@ -4714,10 +4777,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B195" t="s">
-        <v>86</v>
+        <v>275</v>
       </c>
       <c r="C195" t="s">
         <v>5</v>
@@ -4725,10 +4788,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B196" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C196" t="s">
         <v>5</v>
@@ -4736,10 +4799,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B197" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C197" t="s">
         <v>5</v>
@@ -4747,10 +4810,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B198" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="C198" t="s">
         <v>5</v>
@@ -4758,10 +4821,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B199" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C199" t="s">
         <v>5</v>
@@ -4769,10 +4832,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B200" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="C200" t="s">
         <v>5</v>
@@ -4780,10 +4843,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B201" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="C201" t="s">
         <v>5</v>
@@ -4791,10 +4854,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B202" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C202" t="s">
         <v>5</v>
@@ -4802,10 +4865,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B203" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C203" t="s">
         <v>5</v>
@@ -4813,10 +4876,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B204" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C204" t="s">
         <v>5</v>
@@ -4824,10 +4887,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B205" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="C205" t="s">
         <v>5</v>
@@ -4835,10 +4898,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B206" t="s">
-        <v>285</v>
+        <v>7</v>
       </c>
       <c r="C206" t="s">
         <v>5</v>
@@ -4846,10 +4909,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B207" t="s">
-        <v>124</v>
+        <v>4</v>
       </c>
       <c r="C207" t="s">
         <v>5</v>
@@ -4857,10 +4920,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B208" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="C208" t="s">
         <v>5</v>
@@ -4868,10 +4931,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B209" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="C209" t="s">
         <v>5</v>
@@ -4879,10 +4942,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B210" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C210" t="s">
         <v>5</v>
@@ -4890,10 +4953,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B211" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C211" t="s">
         <v>5</v>
@@ -4901,10 +4964,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B212" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="C212" t="s">
         <v>5</v>
@@ -4912,10 +4975,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B213" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C213" t="s">
         <v>5</v>
@@ -4923,10 +4986,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B214" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C214" t="s">
         <v>5</v>
@@ -4934,10 +4997,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B215" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="C215" t="s">
         <v>5</v>
@@ -4945,10 +5008,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B216" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C216" t="s">
         <v>5</v>
@@ -4956,10 +5019,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B217" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C217" t="s">
         <v>5</v>
@@ -4967,10 +5030,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B218" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C218" t="s">
         <v>5</v>
@@ -4978,10 +5041,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B219" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C219" t="s">
         <v>5</v>
@@ -4989,10 +5052,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B220" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C220" t="s">
         <v>5</v>
@@ -5000,10 +5063,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B221" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="C221" t="s">
         <v>5</v>
@@ -5011,10 +5074,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B222" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="C222" t="s">
         <v>5</v>
@@ -5022,10 +5085,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B223" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="C223" t="s">
         <v>5</v>
@@ -5033,10 +5096,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B224" t="s">
-        <v>304</v>
+        <v>94</v>
       </c>
       <c r="C224" t="s">
         <v>5</v>
@@ -5047,7 +5110,7 @@
         <v>305</v>
       </c>
       <c r="B225" t="s">
-        <v>304</v>
+        <v>96</v>
       </c>
       <c r="C225" t="s">
         <v>5</v>
@@ -5058,7 +5121,7 @@
         <v>306</v>
       </c>
       <c r="B226" t="s">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="C226" t="s">
         <v>5</v>
@@ -5080,7 +5143,7 @@
         <v>309</v>
       </c>
       <c r="B228" t="s">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="C228" t="s">
         <v>5</v>
@@ -5091,7 +5154,7 @@
         <v>310</v>
       </c>
       <c r="B229" t="s">
-        <v>311</v>
+        <v>124</v>
       </c>
       <c r="C229" t="s">
         <v>5</v>
@@ -5099,10 +5162,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B230" t="s">
-        <v>9</v>
+        <v>124</v>
       </c>
       <c r="C230" t="s">
         <v>5</v>
@@ -5110,10 +5173,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B231" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C231" t="s">
         <v>5</v>
@@ -5121,10 +5184,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B232" t="s">
-        <v>315</v>
+        <v>12</v>
       </c>
       <c r="C232" t="s">
         <v>5</v>
@@ -5132,10 +5195,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B233" t="s">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="C233" t="s">
         <v>5</v>
@@ -5143,10 +5206,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B234" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="C234" t="s">
         <v>5</v>
@@ -5154,10 +5217,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B235" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C235" t="s">
         <v>5</v>
@@ -5165,10 +5228,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B236" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C236" t="s">
         <v>5</v>
@@ -5176,10 +5239,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B237" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="C237" t="s">
         <v>5</v>
@@ -5187,10 +5250,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B238" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C238" t="s">
         <v>5</v>
@@ -5198,10 +5261,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B239" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="C239" t="s">
         <v>5</v>
@@ -5209,10 +5272,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B240" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -5220,10 +5283,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B241" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C241" t="s">
         <v>5</v>
@@ -5231,10 +5294,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B242" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="C242" t="s">
         <v>5</v>
@@ -5242,10 +5305,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B243" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="C243" t="s">
         <v>5</v>
@@ -5253,10 +5316,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B244" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C244" t="s">
         <v>5</v>
@@ -5264,10 +5327,10 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B245" t="s">
-        <v>61</v>
+        <v>327</v>
       </c>
       <c r="C245" t="s">
         <v>5</v>
@@ -5275,10 +5338,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B246" t="s">
-        <v>37</v>
+        <v>327</v>
       </c>
       <c r="C246" t="s">
         <v>5</v>
@@ -5286,10 +5349,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B247" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C247" t="s">
         <v>5</v>
@@ -5297,10 +5360,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B248" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C248" t="s">
         <v>5</v>
@@ -5308,10 +5371,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B249" t="s">
-        <v>52</v>
+        <v>327</v>
       </c>
       <c r="C249" t="s">
         <v>5</v>
@@ -5319,10 +5382,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
+        <v>332</v>
+      </c>
+      <c r="B250" t="s">
         <v>333</v>
-      </c>
-      <c r="B250" t="s">
-        <v>52</v>
       </c>
       <c r="C250" t="s">
         <v>5</v>
@@ -5333,7 +5396,7 @@
         <v>334</v>
       </c>
       <c r="B251" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C251" t="s">
         <v>5</v>
@@ -5344,7 +5407,7 @@
         <v>335</v>
       </c>
       <c r="B252" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C252" t="s">
         <v>5</v>
@@ -5355,7 +5418,7 @@
         <v>336</v>
       </c>
       <c r="B253" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="C253" t="s">
         <v>5</v>
@@ -5366,7 +5429,7 @@
         <v>337</v>
       </c>
       <c r="B254" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C254" t="s">
         <v>5</v>
@@ -5377,7 +5440,7 @@
         <v>338</v>
       </c>
       <c r="B255" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C255" t="s">
         <v>5</v>
@@ -5388,7 +5451,7 @@
         <v>339</v>
       </c>
       <c r="B256" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="C256" t="s">
         <v>5</v>
@@ -5399,7 +5462,7 @@
         <v>340</v>
       </c>
       <c r="B257" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C257" t="s">
         <v>5</v>
@@ -5410,7 +5473,7 @@
         <v>341</v>
       </c>
       <c r="B258" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C258" t="s">
         <v>5</v>
@@ -5421,7 +5484,7 @@
         <v>342</v>
       </c>
       <c r="B259" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C259" t="s">
         <v>5</v>
@@ -5432,7 +5495,7 @@
         <v>343</v>
       </c>
       <c r="B260" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C260" t="s">
         <v>5</v>
@@ -5443,7 +5506,7 @@
         <v>344</v>
       </c>
       <c r="B261" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C261" t="s">
         <v>5</v>
@@ -5454,7 +5517,7 @@
         <v>345</v>
       </c>
       <c r="B262" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="C262" t="s">
         <v>5</v>
@@ -5465,7 +5528,7 @@
         <v>346</v>
       </c>
       <c r="B263" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="C263" t="s">
         <v>5</v>
@@ -5476,7 +5539,7 @@
         <v>347</v>
       </c>
       <c r="B264" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C264" t="s">
         <v>5</v>
@@ -5487,7 +5550,7 @@
         <v>348</v>
       </c>
       <c r="B265" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C265" t="s">
         <v>5</v>
@@ -5498,7 +5561,7 @@
         <v>349</v>
       </c>
       <c r="B266" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C266" t="s">
         <v>5</v>
@@ -5509,7 +5572,7 @@
         <v>350</v>
       </c>
       <c r="B267" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C267" t="s">
         <v>5</v>
@@ -5520,7 +5583,7 @@
         <v>351</v>
       </c>
       <c r="B268" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="C268" t="s">
         <v>5</v>
@@ -5531,7 +5594,7 @@
         <v>352</v>
       </c>
       <c r="B269" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="C269" t="s">
         <v>5</v>
@@ -5542,7 +5605,7 @@
         <v>353</v>
       </c>
       <c r="B270" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C270" t="s">
         <v>5</v>
@@ -5553,7 +5616,7 @@
         <v>354</v>
       </c>
       <c r="B271" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C271" t="s">
         <v>5</v>
@@ -5564,7 +5627,7 @@
         <v>355</v>
       </c>
       <c r="B272" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C272" t="s">
         <v>5</v>
@@ -5575,7 +5638,7 @@
         <v>356</v>
       </c>
       <c r="B273" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C273" t="s">
         <v>5</v>
@@ -5586,7 +5649,7 @@
         <v>357</v>
       </c>
       <c r="B274" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C274" t="s">
         <v>5</v>
@@ -5597,7 +5660,7 @@
         <v>358</v>
       </c>
       <c r="B275" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="C275" t="s">
         <v>5</v>
@@ -5608,7 +5671,7 @@
         <v>359</v>
       </c>
       <c r="B276" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C276" t="s">
         <v>5</v>
@@ -5619,7 +5682,7 @@
         <v>360</v>
       </c>
       <c r="B277" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="C277" t="s">
         <v>5</v>
@@ -5630,7 +5693,7 @@
         <v>361</v>
       </c>
       <c r="B278" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C278" t="s">
         <v>5</v>
@@ -5641,7 +5704,7 @@
         <v>362</v>
       </c>
       <c r="B279" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C279" t="s">
         <v>5</v>
@@ -5652,7 +5715,7 @@
         <v>363</v>
       </c>
       <c r="B280" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C280" t="s">
         <v>5</v>
@@ -5663,7 +5726,7 @@
         <v>364</v>
       </c>
       <c r="B281" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C281" t="s">
         <v>5</v>
@@ -5674,7 +5737,7 @@
         <v>365</v>
       </c>
       <c r="B282" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C282" t="s">
         <v>5</v>
@@ -5685,7 +5748,7 @@
         <v>366</v>
       </c>
       <c r="B283" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C283" t="s">
         <v>5</v>
@@ -5696,7 +5759,7 @@
         <v>367</v>
       </c>
       <c r="B284" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="C284" t="s">
         <v>5</v>
@@ -5707,7 +5770,7 @@
         <v>368</v>
       </c>
       <c r="B285" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C285" t="s">
         <v>5</v>
@@ -5718,7 +5781,7 @@
         <v>369</v>
       </c>
       <c r="B286" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C286" t="s">
         <v>5</v>
@@ -5729,7 +5792,7 @@
         <v>370</v>
       </c>
       <c r="B287" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C287" t="s">
         <v>5</v>
@@ -5740,7 +5803,7 @@
         <v>371</v>
       </c>
       <c r="B288" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C288" t="s">
         <v>5</v>
@@ -5751,7 +5814,7 @@
         <v>372</v>
       </c>
       <c r="B289" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="C289" t="s">
         <v>5</v>
@@ -5762,7 +5825,7 @@
         <v>373</v>
       </c>
       <c r="B290" t="s">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="C290" t="s">
         <v>5</v>
@@ -5770,10 +5833,10 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B291" t="s">
-        <v>376</v>
+        <v>105</v>
       </c>
       <c r="C291" t="s">
         <v>5</v>
@@ -5781,10 +5844,10 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B292" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="C292" t="s">
         <v>5</v>
@@ -5792,10 +5855,10 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B293" t="s">
-        <v>379</v>
+        <v>15</v>
       </c>
       <c r="C293" t="s">
         <v>5</v>
@@ -5803,10 +5866,10 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B294" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="C294" t="s">
         <v>5</v>
@@ -5814,10 +5877,10 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B295" t="s">
-        <v>252</v>
+        <v>112</v>
       </c>
       <c r="C295" t="s">
         <v>5</v>
@@ -5825,10 +5888,10 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B296" t="s">
-        <v>252</v>
+        <v>15</v>
       </c>
       <c r="C296" t="s">
         <v>5</v>
@@ -5836,10 +5899,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B297" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="C297" t="s">
         <v>5</v>
@@ -5847,10 +5910,10 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B298" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="C298" t="s">
         <v>5</v>
@@ -5858,10 +5921,10 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B299" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -5869,10 +5932,10 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B300" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C300" t="s">
         <v>5</v>
@@ -5880,10 +5943,10 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B301" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C301" t="s">
         <v>5</v>
@@ -5891,10 +5954,10 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B302" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C302" t="s">
         <v>5</v>
@@ -5902,10 +5965,10 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B303" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C303" t="s">
         <v>5</v>
@@ -5913,10 +5976,10 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B304" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C304" t="s">
         <v>5</v>
@@ -5924,10 +5987,10 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B305" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C305" t="s">
         <v>5</v>
@@ -5935,10 +5998,10 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B306" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="C306" t="s">
         <v>5</v>
@@ -5946,10 +6009,10 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B307" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="C307" t="s">
         <v>5</v>
@@ -5957,10 +6020,10 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B308" t="s">
-        <v>395</v>
+        <v>105</v>
       </c>
       <c r="C308" t="s">
         <v>5</v>
@@ -5968,10 +6031,10 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B309" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="C309" t="s">
         <v>5</v>
@@ -5979,10 +6042,10 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B310" t="s">
-        <v>379</v>
+        <v>25</v>
       </c>
       <c r="C310" t="s">
         <v>5</v>
@@ -5990,10 +6053,10 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B311" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="C311" t="s">
         <v>5</v>
@@ -6001,10 +6064,10 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B312" t="s">
-        <v>141</v>
+        <v>397</v>
       </c>
       <c r="C312" t="s">
         <v>5</v>
@@ -6012,10 +6075,10 @@
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B313" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="C313" t="s">
         <v>5</v>
@@ -6023,10 +6086,10 @@
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B314" t="s">
-        <v>226</v>
+        <v>400</v>
       </c>
       <c r="C314" t="s">
         <v>5</v>
@@ -6034,10 +6097,10 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B315" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="C315" t="s">
         <v>5</v>
@@ -6045,10 +6108,10 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B316" t="s">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="C316" t="s">
         <v>5</v>
@@ -6056,10 +6119,10 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B317" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="C317" t="s">
         <v>5</v>
@@ -6067,10 +6130,10 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B318" t="s">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="C318" t="s">
         <v>5</v>
@@ -6078,10 +6141,10 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B319" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="C319" t="s">
         <v>5</v>
@@ -6089,10 +6152,10 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B320" t="s">
-        <v>374</v>
+        <v>23</v>
       </c>
       <c r="C320" t="s">
         <v>5</v>
@@ -6100,10 +6163,10 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B321" t="s">
-        <v>285</v>
+        <v>23</v>
       </c>
       <c r="C321" t="s">
         <v>5</v>
@@ -6111,10 +6174,10 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B322" t="s">
-        <v>285</v>
+        <v>23</v>
       </c>
       <c r="C322" t="s">
         <v>5</v>
@@ -6122,10 +6185,10 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B323" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="C323" t="s">
         <v>5</v>
@@ -6133,10 +6196,10 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B324" t="s">
-        <v>379</v>
+        <v>124</v>
       </c>
       <c r="C324" t="s">
         <v>5</v>
@@ -6144,10 +6207,10 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B325" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C325" t="s">
         <v>5</v>
@@ -6155,10 +6218,10 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B326" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C326" t="s">
         <v>5</v>
@@ -6166,10 +6229,10 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B327" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C327" t="s">
         <v>5</v>
@@ -6177,10 +6240,10 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B328" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C328" t="s">
         <v>5</v>
@@ -6188,10 +6251,10 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
+        <v>415</v>
+      </c>
+      <c r="B329" t="s">
         <v>416</v>
-      </c>
-      <c r="B329" t="s">
-        <v>76</v>
       </c>
       <c r="C329" t="s">
         <v>5</v>
@@ -6202,7 +6265,7 @@
         <v>417</v>
       </c>
       <c r="B330" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C330" t="s">
         <v>5</v>
@@ -6213,7 +6276,7 @@
         <v>418</v>
       </c>
       <c r="B331" t="s">
-        <v>37</v>
+        <v>400</v>
       </c>
       <c r="C331" t="s">
         <v>5</v>
@@ -6224,7 +6287,7 @@
         <v>419</v>
       </c>
       <c r="B332" t="s">
-        <v>42</v>
+        <v>400</v>
       </c>
       <c r="C332" t="s">
         <v>5</v>
@@ -6235,7 +6298,7 @@
         <v>420</v>
       </c>
       <c r="B333" t="s">
-        <v>39</v>
+        <v>164</v>
       </c>
       <c r="C333" t="s">
         <v>5</v>
@@ -6246,7 +6309,7 @@
         <v>421</v>
       </c>
       <c r="B334" t="s">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="C334" t="s">
         <v>5</v>
@@ -6257,7 +6320,7 @@
         <v>422</v>
       </c>
       <c r="B335" t="s">
-        <v>61</v>
+        <v>249</v>
       </c>
       <c r="C335" t="s">
         <v>5</v>
@@ -6268,7 +6331,7 @@
         <v>423</v>
       </c>
       <c r="B336" t="s">
-        <v>61</v>
+        <v>161</v>
       </c>
       <c r="C336" t="s">
         <v>5</v>
@@ -6279,7 +6342,7 @@
         <v>424</v>
       </c>
       <c r="B337" t="s">
-        <v>86</v>
+        <v>247</v>
       </c>
       <c r="C337" t="s">
         <v>5</v>
@@ -6290,7 +6353,7 @@
         <v>425</v>
       </c>
       <c r="B338" t="s">
-        <v>64</v>
+        <v>254</v>
       </c>
       <c r="C338" t="s">
         <v>5</v>
@@ -6301,7 +6364,7 @@
         <v>426</v>
       </c>
       <c r="B339" t="s">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="C339" t="s">
         <v>5</v>
@@ -6312,7 +6375,7 @@
         <v>427</v>
       </c>
       <c r="B340" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="C340" t="s">
         <v>5</v>
@@ -6323,7 +6386,7 @@
         <v>428</v>
       </c>
       <c r="B341" t="s">
-        <v>112</v>
+        <v>395</v>
       </c>
       <c r="C341" t="s">
         <v>5</v>
@@ -6334,7 +6397,7 @@
         <v>429</v>
       </c>
       <c r="B342" t="s">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="C342" t="s">
         <v>5</v>
@@ -6345,7 +6408,7 @@
         <v>430</v>
       </c>
       <c r="B343" t="s">
-        <v>97</v>
+        <v>308</v>
       </c>
       <c r="C343" t="s">
         <v>5</v>
@@ -6356,7 +6419,7 @@
         <v>431</v>
       </c>
       <c r="B344" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="C344" t="s">
         <v>5</v>
@@ -6367,7 +6430,7 @@
         <v>432</v>
       </c>
       <c r="B345" t="s">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="C345" t="s">
         <v>5</v>
@@ -6378,7 +6441,7 @@
         <v>433</v>
       </c>
       <c r="B346" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="C346" t="s">
         <v>5</v>
@@ -6389,7 +6452,7 @@
         <v>434</v>
       </c>
       <c r="B347" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="C347" t="s">
         <v>5</v>
@@ -6400,7 +6463,7 @@
         <v>435</v>
       </c>
       <c r="B348" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="C348" t="s">
         <v>5</v>
@@ -6411,7 +6474,7 @@
         <v>436</v>
       </c>
       <c r="B349" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="C349" t="s">
         <v>5</v>
@@ -6422,7 +6485,7 @@
         <v>437</v>
       </c>
       <c r="B350" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C350" t="s">
         <v>5</v>
@@ -6433,7 +6496,7 @@
         <v>438</v>
       </c>
       <c r="B351" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C351" t="s">
         <v>5</v>
@@ -6444,7 +6507,7 @@
         <v>439</v>
       </c>
       <c r="B352" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="C352" t="s">
         <v>5</v>
@@ -6455,7 +6518,7 @@
         <v>440</v>
       </c>
       <c r="B353" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="C353" t="s">
         <v>5</v>
@@ -6466,7 +6529,7 @@
         <v>441</v>
       </c>
       <c r="B354" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C354" t="s">
         <v>5</v>
@@ -6477,7 +6540,7 @@
         <v>442</v>
       </c>
       <c r="B355" t="s">
-        <v>374</v>
+        <v>7</v>
       </c>
       <c r="C355" t="s">
         <v>5</v>
@@ -6488,7 +6551,7 @@
         <v>443</v>
       </c>
       <c r="B356" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C356" t="s">
         <v>5</v>
@@ -6499,7 +6562,7 @@
         <v>444</v>
       </c>
       <c r="B357" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C357" t="s">
         <v>5</v>
@@ -6510,7 +6573,7 @@
         <v>445</v>
       </c>
       <c r="B358" t="s">
-        <v>124</v>
+        <v>12</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -6521,7 +6584,7 @@
         <v>446</v>
       </c>
       <c r="B359" t="s">
-        <v>285</v>
+        <v>94</v>
       </c>
       <c r="C359" t="s">
         <v>5</v>
@@ -6532,7 +6595,7 @@
         <v>447</v>
       </c>
       <c r="B360" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="C360" t="s">
         <v>5</v>
@@ -6543,7 +6606,7 @@
         <v>448</v>
       </c>
       <c r="B361" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="C361" t="s">
         <v>5</v>
@@ -6554,7 +6617,7 @@
         <v>449</v>
       </c>
       <c r="B362" t="s">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="C362" t="s">
         <v>5</v>
@@ -6565,7 +6628,7 @@
         <v>450</v>
       </c>
       <c r="B363" t="s">
-        <v>379</v>
+        <v>23</v>
       </c>
       <c r="C363" t="s">
         <v>5</v>
@@ -6576,7 +6639,7 @@
         <v>451</v>
       </c>
       <c r="B364" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C364" t="s">
         <v>5</v>
@@ -6587,7 +6650,7 @@
         <v>452</v>
       </c>
       <c r="B365" t="s">
-        <v>395</v>
+        <v>23</v>
       </c>
       <c r="C365" t="s">
         <v>5</v>
@@ -6598,7 +6661,7 @@
         <v>453</v>
       </c>
       <c r="B366" t="s">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="C366" t="s">
         <v>5</v>
@@ -6609,7 +6672,7 @@
         <v>454</v>
       </c>
       <c r="B367" t="s">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="C367" t="s">
         <v>5</v>
@@ -6620,7 +6683,7 @@
         <v>455</v>
       </c>
       <c r="B368" t="s">
-        <v>374</v>
+        <v>25</v>
       </c>
       <c r="C368" t="s">
         <v>5</v>
@@ -6631,7 +6694,7 @@
         <v>456</v>
       </c>
       <c r="B369" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="C369" t="s">
         <v>5</v>
@@ -6642,7 +6705,7 @@
         <v>457</v>
       </c>
       <c r="B370" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C370" t="s">
         <v>5</v>
@@ -6653,7 +6716,7 @@
         <v>458</v>
       </c>
       <c r="B371" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C371" t="s">
         <v>5</v>
@@ -6664,7 +6727,7 @@
         <v>459</v>
       </c>
       <c r="B372" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C372" t="s">
         <v>5</v>
@@ -6675,7 +6738,7 @@
         <v>460</v>
       </c>
       <c r="B373" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="C373" t="s">
         <v>5</v>
@@ -6686,7 +6749,7 @@
         <v>461</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>112</v>
       </c>
       <c r="C374" t="s">
         <v>5</v>
@@ -6697,7 +6760,7 @@
         <v>462</v>
       </c>
       <c r="B375" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C375" t="s">
         <v>5</v>
@@ -6708,7 +6771,7 @@
         <v>463</v>
       </c>
       <c r="B376" t="s">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="C376" t="s">
         <v>5</v>
@@ -6719,7 +6782,7 @@
         <v>464</v>
       </c>
       <c r="B377" t="s">
-        <v>285</v>
+        <v>126</v>
       </c>
       <c r="C377" t="s">
         <v>5</v>
@@ -6730,7 +6793,7 @@
         <v>465</v>
       </c>
       <c r="B378" t="s">
-        <v>285</v>
+        <v>109</v>
       </c>
       <c r="C378" t="s">
         <v>5</v>
@@ -6741,7 +6804,7 @@
         <v>466</v>
       </c>
       <c r="B379" t="s">
-        <v>395</v>
+        <v>17</v>
       </c>
       <c r="C379" t="s">
         <v>5</v>
@@ -6752,7 +6815,7 @@
         <v>467</v>
       </c>
       <c r="B380" t="s">
-        <v>252</v>
+        <v>308</v>
       </c>
       <c r="C380" t="s">
         <v>5</v>
@@ -6763,7 +6826,7 @@
         <v>468</v>
       </c>
       <c r="B381" t="s">
-        <v>379</v>
+        <v>19</v>
       </c>
       <c r="C381" t="s">
         <v>5</v>
@@ -6774,7 +6837,7 @@
         <v>469</v>
       </c>
       <c r="B382" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="C382" t="s">
         <v>5</v>
@@ -6785,7 +6848,7 @@
         <v>470</v>
       </c>
       <c r="B383" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C383" t="s">
         <v>5</v>
@@ -6796,7 +6859,7 @@
         <v>471</v>
       </c>
       <c r="B384" t="s">
-        <v>148</v>
+        <v>400</v>
       </c>
       <c r="C384" t="s">
         <v>5</v>
@@ -6807,7 +6870,7 @@
         <v>472</v>
       </c>
       <c r="B385" t="s">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="C385" t="s">
         <v>5</v>
@@ -6818,7 +6881,7 @@
         <v>473</v>
       </c>
       <c r="B386" t="s">
-        <v>159</v>
+        <v>416</v>
       </c>
       <c r="C386" t="s">
         <v>5</v>
@@ -6829,7 +6892,7 @@
         <v>474</v>
       </c>
       <c r="B387" t="s">
-        <v>141</v>
+        <v>275</v>
       </c>
       <c r="C387" t="s">
         <v>5</v>
@@ -6840,7 +6903,7 @@
         <v>475</v>
       </c>
       <c r="B388" t="s">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="C388" t="s">
         <v>5</v>
@@ -6851,7 +6914,7 @@
         <v>476</v>
       </c>
       <c r="B389" t="s">
-        <v>477</v>
+        <v>395</v>
       </c>
       <c r="C389" t="s">
         <v>5</v>
@@ -6859,10 +6922,10 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B390" t="s">
-        <v>479</v>
+        <v>109</v>
       </c>
       <c r="C390" t="s">
         <v>5</v>
@@ -6870,10 +6933,10 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B391" t="s">
-        <v>228</v>
+        <v>126</v>
       </c>
       <c r="C391" t="s">
         <v>5</v>
@@ -6881,10 +6944,10 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B392" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="C392" t="s">
         <v>5</v>
@@ -6892,10 +6955,10 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B393" t="s">
-        <v>143</v>
+        <v>15</v>
       </c>
       <c r="C393" t="s">
         <v>5</v>
@@ -6903,10 +6966,10 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B394" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C394" t="s">
         <v>5</v>
@@ -6914,10 +6977,10 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B395" t="s">
-        <v>112</v>
+        <v>395</v>
       </c>
       <c r="C395" t="s">
         <v>5</v>
@@ -6925,10 +6988,10 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B396" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="C396" t="s">
         <v>5</v>
@@ -6936,10 +6999,10 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B397" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="C397" t="s">
         <v>5</v>
@@ -6947,10 +7010,10 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B398" t="s">
-        <v>76</v>
+        <v>308</v>
       </c>
       <c r="C398" t="s">
         <v>5</v>
@@ -6958,10 +7021,10 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B399" t="s">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="C399" t="s">
         <v>5</v>
@@ -6969,10 +7032,10 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B400" t="s">
-        <v>70</v>
+        <v>416</v>
       </c>
       <c r="C400" t="s">
         <v>5</v>
@@ -6980,10 +7043,10 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B401" t="s">
-        <v>83</v>
+        <v>275</v>
       </c>
       <c r="C401" t="s">
         <v>5</v>
@@ -6991,10 +7054,10 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B402" t="s">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="C402" t="s">
         <v>5</v>
@@ -7002,10 +7065,10 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B403" t="s">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="C403" t="s">
         <v>5</v>
@@ -7013,10 +7076,10 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B404" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="C404" t="s">
         <v>5</v>
@@ -7024,10 +7087,10 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B405" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="C405" t="s">
         <v>5</v>
@@ -7035,10 +7098,10 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B406" t="s">
-        <v>23</v>
+        <v>270</v>
       </c>
       <c r="C406" t="s">
         <v>5</v>
@@ -7046,10 +7109,10 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B407" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="C407" t="s">
         <v>5</v>
@@ -7057,10 +7120,10 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B408" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="C408" t="s">
         <v>5</v>
@@ -7068,10 +7131,10 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B409" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="C409" t="s">
         <v>5</v>
@@ -7079,10 +7142,10 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B410" t="s">
-        <v>97</v>
+        <v>498</v>
       </c>
       <c r="C410" t="s">
         <v>5</v>
@@ -7090,10 +7153,10 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
+        <v>499</v>
+      </c>
+      <c r="B411" t="s">
         <v>500</v>
-      </c>
-      <c r="B411" t="s">
-        <v>124</v>
       </c>
       <c r="C411" t="s">
         <v>5</v>
@@ -7104,7 +7167,7 @@
         <v>501</v>
       </c>
       <c r="B412" t="s">
-        <v>66</v>
+        <v>251</v>
       </c>
       <c r="C412" t="s">
         <v>5</v>
@@ -7115,7 +7178,7 @@
         <v>502</v>
       </c>
       <c r="B413" t="s">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="C413" t="s">
         <v>5</v>
@@ -7126,7 +7189,7 @@
         <v>503</v>
       </c>
       <c r="B414" t="s">
-        <v>64</v>
+        <v>166</v>
       </c>
       <c r="C414" t="s">
         <v>5</v>
@@ -7137,7 +7200,7 @@
         <v>504</v>
       </c>
       <c r="B415" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C415" t="s">
         <v>5</v>
@@ -7159,7 +7222,7 @@
         <v>506</v>
       </c>
       <c r="B417" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -7170,7 +7233,7 @@
         <v>507</v>
       </c>
       <c r="B418" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="C418" t="s">
         <v>5</v>
@@ -7181,7 +7244,7 @@
         <v>508</v>
       </c>
       <c r="B419" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C419" t="s">
         <v>5</v>
@@ -7192,7 +7255,7 @@
         <v>509</v>
       </c>
       <c r="B420" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="C420" t="s">
         <v>5</v>
@@ -7203,7 +7266,7 @@
         <v>510</v>
       </c>
       <c r="B421" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="C421" t="s">
         <v>5</v>
@@ -7214,7 +7277,7 @@
         <v>511</v>
       </c>
       <c r="B422" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C422" t="s">
         <v>5</v>
@@ -7225,7 +7288,7 @@
         <v>512</v>
       </c>
       <c r="B423" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="C423" t="s">
         <v>5</v>
@@ -7236,7 +7299,7 @@
         <v>513</v>
       </c>
       <c r="B424" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C424" t="s">
         <v>5</v>
@@ -7247,7 +7310,7 @@
         <v>514</v>
       </c>
       <c r="B425" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C425" t="s">
         <v>5</v>
@@ -7258,7 +7321,7 @@
         <v>515</v>
       </c>
       <c r="B426" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C426" t="s">
         <v>5</v>
@@ -7269,7 +7332,7 @@
         <v>516</v>
       </c>
       <c r="B427" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="C427" t="s">
         <v>5</v>
@@ -7280,7 +7343,7 @@
         <v>517</v>
       </c>
       <c r="B428" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C428" t="s">
         <v>5</v>
@@ -7302,7 +7365,7 @@
         <v>519</v>
       </c>
       <c r="B430" t="s">
-        <v>131</v>
+        <v>12</v>
       </c>
       <c r="C430" t="s">
         <v>5</v>
@@ -7313,7 +7376,7 @@
         <v>520</v>
       </c>
       <c r="B431" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C431" t="s">
         <v>5</v>
@@ -7324,7 +7387,7 @@
         <v>521</v>
       </c>
       <c r="B432" t="s">
-        <v>374</v>
+        <v>17</v>
       </c>
       <c r="C432" t="s">
         <v>5</v>
@@ -7335,7 +7398,7 @@
         <v>522</v>
       </c>
       <c r="B433" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C433" t="s">
         <v>5</v>
@@ -7346,7 +7409,7 @@
         <v>523</v>
       </c>
       <c r="B434" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="C434" t="s">
         <v>5</v>
@@ -7357,7 +7420,7 @@
         <v>524</v>
       </c>
       <c r="B435" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="C435" t="s">
         <v>5</v>
@@ -7368,7 +7431,7 @@
         <v>525</v>
       </c>
       <c r="B436" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="C436" t="s">
         <v>5</v>
@@ -7379,7 +7442,7 @@
         <v>526</v>
       </c>
       <c r="B437" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="C437" t="s">
         <v>5</v>
@@ -7390,7 +7453,7 @@
         <v>527</v>
       </c>
       <c r="B438" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C438" t="s">
         <v>5</v>
@@ -7401,7 +7464,7 @@
         <v>528</v>
       </c>
       <c r="B439" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="C439" t="s">
         <v>5</v>
@@ -7412,7 +7475,7 @@
         <v>529</v>
       </c>
       <c r="B440" t="s">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="C440" t="s">
         <v>5</v>
@@ -7423,7 +7486,7 @@
         <v>530</v>
       </c>
       <c r="B441" t="s">
-        <v>395</v>
+        <v>96</v>
       </c>
       <c r="C441" t="s">
         <v>5</v>
@@ -7434,7 +7497,7 @@
         <v>531</v>
       </c>
       <c r="B442" t="s">
-        <v>395</v>
+        <v>96</v>
       </c>
       <c r="C442" t="s">
         <v>5</v>
@@ -7445,7 +7508,7 @@
         <v>532</v>
       </c>
       <c r="B443" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="C443" t="s">
         <v>5</v>
@@ -7456,7 +7519,7 @@
         <v>533</v>
       </c>
       <c r="B444" t="s">
-        <v>285</v>
+        <v>15</v>
       </c>
       <c r="C444" t="s">
         <v>5</v>
@@ -7467,7 +7530,7 @@
         <v>534</v>
       </c>
       <c r="B445" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C445" t="s">
         <v>5</v>
@@ -7478,7 +7541,7 @@
         <v>535</v>
       </c>
       <c r="B446" t="s">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="C446" t="s">
         <v>5</v>
@@ -7489,7 +7552,7 @@
         <v>536</v>
       </c>
       <c r="B447" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="C447" t="s">
         <v>5</v>
@@ -7500,7 +7563,7 @@
         <v>537</v>
       </c>
       <c r="B448" t="s">
-        <v>376</v>
+        <v>23</v>
       </c>
       <c r="C448" t="s">
         <v>5</v>
@@ -7511,7 +7574,7 @@
         <v>538</v>
       </c>
       <c r="B449" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="C449" t="s">
         <v>5</v>
@@ -7522,7 +7585,7 @@
         <v>539</v>
       </c>
       <c r="B450" t="s">
-        <v>379</v>
+        <v>126</v>
       </c>
       <c r="C450" t="s">
         <v>5</v>
@@ -7533,7 +7596,7 @@
         <v>540</v>
       </c>
       <c r="B451" t="s">
-        <v>376</v>
+        <v>19</v>
       </c>
       <c r="C451" t="s">
         <v>5</v>
@@ -7544,7 +7607,7 @@
         <v>541</v>
       </c>
       <c r="B452" t="s">
-        <v>542</v>
+        <v>153</v>
       </c>
       <c r="C452" t="s">
         <v>5</v>
@@ -7552,10 +7615,10 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B453" t="s">
-        <v>138</v>
+        <v>395</v>
       </c>
       <c r="C453" t="s">
         <v>5</v>
@@ -7563,10 +7626,10 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B454" t="s">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="C454" t="s">
         <v>5</v>
@@ -7574,10 +7637,10 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B455" t="s">
-        <v>148</v>
+        <v>15</v>
       </c>
       <c r="C455" t="s">
         <v>5</v>
@@ -7585,10 +7648,10 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B456" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="C456" t="s">
         <v>5</v>
@@ -7596,10 +7659,10 @@
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B457" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C457" t="s">
         <v>5</v>
@@ -7607,10 +7670,10 @@
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B458" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C458" t="s">
         <v>5</v>
@@ -7618,10 +7681,10 @@
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B459" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="C459" t="s">
         <v>5</v>
@@ -7629,10 +7692,10 @@
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B460" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="C460" t="s">
         <v>5</v>
@@ -7640,10 +7703,10 @@
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B461" t="s">
-        <v>169</v>
+        <v>416</v>
       </c>
       <c r="C461" t="s">
         <v>5</v>
@@ -7651,10 +7714,10 @@
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B462" t="s">
-        <v>135</v>
+        <v>416</v>
       </c>
       <c r="C462" t="s">
         <v>5</v>
@@ -7662,10 +7725,10 @@
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B463" t="s">
-        <v>169</v>
+        <v>416</v>
       </c>
       <c r="C463" t="s">
         <v>5</v>
@@ -7673,10 +7736,10 @@
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B464" t="s">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="C464" t="s">
         <v>5</v>
@@ -7684,10 +7747,10 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B465" t="s">
-        <v>131</v>
+        <v>308</v>
       </c>
       <c r="C465" t="s">
         <v>5</v>
@@ -7695,10 +7758,10 @@
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B466" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="C466" t="s">
         <v>5</v>
@@ -7706,10 +7769,10 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B467" t="s">
-        <v>80</v>
+        <v>275</v>
       </c>
       <c r="C467" t="s">
         <v>5</v>
@@ -7717,10 +7780,10 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B468" t="s">
-        <v>374</v>
+        <v>153</v>
       </c>
       <c r="C468" t="s">
         <v>5</v>
@@ -7728,10 +7791,10 @@
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B469" t="s">
-        <v>285</v>
+        <v>397</v>
       </c>
       <c r="C469" t="s">
         <v>5</v>
@@ -7739,10 +7802,10 @@
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B470" t="s">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="C470" t="s">
         <v>5</v>
@@ -7750,10 +7813,10 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B471" t="s">
-        <v>131</v>
+        <v>400</v>
       </c>
       <c r="C471" t="s">
         <v>5</v>
@@ -7761,10 +7824,10 @@
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B472" t="s">
-        <v>252</v>
+        <v>397</v>
       </c>
       <c r="C472" t="s">
         <v>5</v>
@@ -7772,10 +7835,10 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
+        <v>562</v>
+      </c>
+      <c r="B473" t="s">
         <v>563</v>
-      </c>
-      <c r="B473" t="s">
-        <v>129</v>
       </c>
       <c r="C473" t="s">
         <v>5</v>
@@ -7786,7 +7849,7 @@
         <v>564</v>
       </c>
       <c r="B474" t="s">
-        <v>395</v>
+        <v>161</v>
       </c>
       <c r="C474" t="s">
         <v>5</v>
@@ -7797,7 +7860,7 @@
         <v>565</v>
       </c>
       <c r="B475" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
       <c r="C475" t="s">
         <v>5</v>
@@ -7808,7 +7871,7 @@
         <v>566</v>
       </c>
       <c r="B476" t="s">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -7819,7 +7882,7 @@
         <v>567</v>
       </c>
       <c r="B477" t="s">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="C477" t="s">
         <v>5</v>
@@ -7830,7 +7893,7 @@
         <v>568</v>
       </c>
       <c r="B478" t="s">
-        <v>226</v>
+        <v>153</v>
       </c>
       <c r="C478" t="s">
         <v>5</v>
@@ -7841,7 +7904,7 @@
         <v>569</v>
       </c>
       <c r="B479" t="s">
-        <v>477</v>
+        <v>19</v>
       </c>
       <c r="C479" t="s">
         <v>5</v>
@@ -7852,7 +7915,7 @@
         <v>570</v>
       </c>
       <c r="B480" t="s">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="C480" t="s">
         <v>5</v>
@@ -7863,7 +7926,7 @@
         <v>571</v>
       </c>
       <c r="B481" t="s">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="C481" t="s">
         <v>5</v>
@@ -7874,7 +7937,7 @@
         <v>572</v>
       </c>
       <c r="B482" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="C482" t="s">
         <v>5</v>
@@ -7885,7 +7948,7 @@
         <v>573</v>
       </c>
       <c r="B483" t="s">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="C483" t="s">
         <v>5</v>
@@ -7896,7 +7959,7 @@
         <v>574</v>
       </c>
       <c r="B484" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="C484" t="s">
         <v>5</v>
@@ -7907,7 +7970,7 @@
         <v>575</v>
       </c>
       <c r="B485" t="s">
-        <v>176</v>
+        <v>270</v>
       </c>
       <c r="C485" t="s">
         <v>5</v>
@@ -7918,7 +7981,7 @@
         <v>576</v>
       </c>
       <c r="B486" t="s">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="C486" t="s">
         <v>5</v>
@@ -7929,7 +7992,7 @@
         <v>577</v>
       </c>
       <c r="B487" t="s">
-        <v>242</v>
+        <v>109</v>
       </c>
       <c r="C487" t="s">
         <v>5</v>
@@ -7940,7 +8003,7 @@
         <v>578</v>
       </c>
       <c r="B488" t="s">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="C488" t="s">
         <v>5</v>
@@ -7951,7 +8014,7 @@
         <v>579</v>
       </c>
       <c r="B489" t="s">
-        <v>580</v>
+        <v>395</v>
       </c>
       <c r="C489" t="s">
         <v>5</v>
@@ -7959,10 +8022,10 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B490" t="s">
-        <v>580</v>
+        <v>308</v>
       </c>
       <c r="C490" t="s">
         <v>5</v>
@@ -7970,10 +8033,10 @@
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B491" t="s">
-        <v>580</v>
+        <v>308</v>
       </c>
       <c r="C491" t="s">
         <v>5</v>
@@ -7981,10 +8044,10 @@
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B492" t="s">
-        <v>580</v>
+        <v>19</v>
       </c>
       <c r="C492" t="s">
         <v>5</v>
@@ -7992,10 +8055,10 @@
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B493" t="s">
-        <v>585</v>
+        <v>275</v>
       </c>
       <c r="C493" t="s">
         <v>5</v>
@@ -8003,10 +8066,10 @@
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B494" t="s">
-        <v>587</v>
+        <v>153</v>
       </c>
       <c r="C494" t="s">
         <v>5</v>
@@ -8014,10 +8077,10 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B495" t="s">
-        <v>188</v>
+        <v>416</v>
       </c>
       <c r="C495" t="s">
         <v>5</v>
@@ -8025,10 +8088,10 @@
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B496" t="s">
-        <v>580</v>
+        <v>153</v>
       </c>
       <c r="C496" t="s">
         <v>5</v>
@@ -8036,10 +8099,10 @@
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B497" t="s">
-        <v>220</v>
+        <v>153</v>
       </c>
       <c r="C497" t="s">
         <v>5</v>
@@ -8047,10 +8110,10 @@
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B498" t="s">
-        <v>585</v>
+        <v>251</v>
       </c>
       <c r="C498" t="s">
         <v>5</v>
@@ -8058,10 +8121,10 @@
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B499" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C499" t="s">
         <v>5</v>
@@ -8069,10 +8132,10 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B500" t="s">
-        <v>594</v>
+        <v>498</v>
       </c>
       <c r="C500" t="s">
         <v>5</v>
@@ -8080,10 +8143,10 @@
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B501" t="s">
-        <v>594</v>
+        <v>247</v>
       </c>
       <c r="C501" t="s">
         <v>5</v>
@@ -8091,10 +8154,10 @@
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B502" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="C502" t="s">
         <v>5</v>
@@ -8102,10 +8165,10 @@
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B503" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="C503" t="s">
         <v>5</v>
@@ -8113,10 +8176,10 @@
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B504" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="C504" t="s">
         <v>5</v>
@@ -8124,10 +8187,10 @@
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B505" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="C505" t="s">
         <v>5</v>
@@ -8135,10 +8198,10 @@
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B506" t="s">
-        <v>601</v>
+        <v>199</v>
       </c>
       <c r="C506" t="s">
         <v>5</v>
@@ -8146,10 +8209,10 @@
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B507" t="s">
-        <v>601</v>
+        <v>199</v>
       </c>
       <c r="C507" t="s">
         <v>5</v>
@@ -8157,10 +8220,10 @@
     </row>
     <row r="508">
       <c r="A508" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B508" t="s">
-        <v>604</v>
+        <v>265</v>
       </c>
       <c r="C508" t="s">
         <v>5</v>
@@ -8168,10 +8231,10 @@
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="B509" t="s">
-        <v>606</v>
+        <v>204</v>
       </c>
       <c r="C509" t="s">
         <v>5</v>
@@ -8179,10 +8242,10 @@
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="B510" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="C510" t="s">
         <v>5</v>
@@ -8190,10 +8253,10 @@
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="B511" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="C511" t="s">
         <v>5</v>
@@ -8201,10 +8264,10 @@
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B512" t="s">
-        <v>197</v>
+        <v>601</v>
       </c>
       <c r="C512" t="s">
         <v>5</v>
@@ -8212,10 +8275,10 @@
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="B513" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="C513" t="s">
         <v>5</v>
@@ -8223,10 +8286,10 @@
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="B514" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="C514" t="s">
         <v>5</v>
@@ -8234,10 +8297,10 @@
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B515" t="s">
-        <v>209</v>
+        <v>608</v>
       </c>
       <c r="C515" t="s">
         <v>5</v>
@@ -8245,10 +8308,10 @@
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="B516" t="s">
-        <v>618</v>
+        <v>211</v>
       </c>
       <c r="C516" t="s">
         <v>5</v>
@@ -8256,10 +8319,10 @@
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="B517" t="s">
-        <v>195</v>
+        <v>601</v>
       </c>
       <c r="C517" t="s">
         <v>5</v>
@@ -8267,10 +8330,10 @@
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="B518" t="s">
-        <v>621</v>
+        <v>243</v>
       </c>
       <c r="C518" t="s">
         <v>5</v>
@@ -8278,10 +8341,10 @@
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="B519" t="s">
-        <v>623</v>
+        <v>606</v>
       </c>
       <c r="C519" t="s">
         <v>5</v>
@@ -8289,10 +8352,10 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="B520" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C520" t="s">
         <v>5</v>
@@ -8300,10 +8363,10 @@
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="B521" t="s">
-        <v>218</v>
+        <v>615</v>
       </c>
       <c r="C521" t="s">
         <v>5</v>
@@ -8311,10 +8374,10 @@
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="B522" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="C522" t="s">
         <v>5</v>
@@ -8322,10 +8385,10 @@
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="B523" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C523" t="s">
         <v>5</v>
@@ -8333,10 +8396,10 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="B524" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C524" t="s">
         <v>5</v>
@@ -8344,10 +8407,10 @@
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="B525" t="s">
-        <v>630</v>
+        <v>227</v>
       </c>
       <c r="C525" t="s">
         <v>5</v>
@@ -8355,10 +8418,10 @@
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="B526" t="s">
-        <v>632</v>
+        <v>239</v>
       </c>
       <c r="C526" t="s">
         <v>5</v>
@@ -8366,10 +8429,10 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="B527" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="C527" t="s">
         <v>5</v>
@@ -8377,10 +8440,10 @@
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="B528" t="s">
-        <v>193</v>
+        <v>622</v>
       </c>
       <c r="C528" t="s">
         <v>5</v>
@@ -8388,10 +8451,10 @@
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="B529" t="s">
-        <v>218</v>
+        <v>625</v>
       </c>
       <c r="C529" t="s">
         <v>5</v>
@@ -8399,10 +8462,10 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="B530" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="C530" t="s">
         <v>5</v>
@@ -8410,10 +8473,10 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="B531" t="s">
-        <v>193</v>
+        <v>629</v>
       </c>
       <c r="C531" t="s">
         <v>5</v>
@@ -8421,10 +8484,10 @@
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="B532" t="s">
-        <v>621</v>
+        <v>631</v>
       </c>
       <c r="C532" t="s">
         <v>5</v>
@@ -8432,10 +8495,10 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="B533" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="C533" t="s">
         <v>5</v>
@@ -8443,10 +8506,10 @@
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="B534" t="s">
-        <v>218</v>
+        <v>634</v>
       </c>
       <c r="C534" t="s">
         <v>5</v>
@@ -8454,10 +8517,10 @@
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="B535" t="s">
-        <v>188</v>
+        <v>636</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -8465,10 +8528,10 @@
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="B536" t="s">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="C536" t="s">
         <v>5</v>
@@ -8476,10 +8539,10 @@
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B537" t="s">
-        <v>183</v>
+        <v>639</v>
       </c>
       <c r="C537" t="s">
         <v>5</v>
@@ -8487,10 +8550,10 @@
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="B538" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C538" t="s">
         <v>5</v>
@@ -8498,10 +8561,10 @@
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="B539" t="s">
-        <v>156</v>
+        <v>642</v>
       </c>
       <c r="C539" t="s">
         <v>5</v>
@@ -8509,10 +8572,10 @@
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="B540" t="s">
-        <v>156</v>
+        <v>644</v>
       </c>
       <c r="C540" t="s">
         <v>5</v>
@@ -8520,10 +8583,10 @@
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B541" t="s">
-        <v>477</v>
+        <v>241</v>
       </c>
       <c r="C541" t="s">
         <v>5</v>
@@ -8531,10 +8594,10 @@
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B542" t="s">
-        <v>156</v>
+        <v>241</v>
       </c>
       <c r="C542" t="s">
         <v>5</v>
@@ -8542,10 +8605,10 @@
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B543" t="s">
-        <v>226</v>
+        <v>642</v>
       </c>
       <c r="C543" t="s">
         <v>5</v>
@@ -8553,10 +8616,10 @@
     </row>
     <row r="544">
       <c r="A544" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B544" t="s">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="C544" t="s">
         <v>5</v>
@@ -8564,10 +8627,10 @@
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B545" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C545" t="s">
         <v>5</v>
@@ -8575,10 +8638,10 @@
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B546" t="s">
-        <v>159</v>
+        <v>651</v>
       </c>
       <c r="C546" t="s">
         <v>5</v>
@@ -8586,10 +8649,10 @@
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B547" t="s">
-        <v>138</v>
+        <v>653</v>
       </c>
       <c r="C547" t="s">
         <v>5</v>
@@ -8597,10 +8660,10 @@
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B548" t="s">
-        <v>145</v>
+        <v>655</v>
       </c>
       <c r="C548" t="s">
         <v>5</v>
@@ -8608,10 +8671,10 @@
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B549" t="s">
-        <v>542</v>
+        <v>216</v>
       </c>
       <c r="C549" t="s">
         <v>5</v>
@@ -8619,10 +8682,10 @@
     </row>
     <row r="550">
       <c r="A550" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B550" t="s">
-        <v>138</v>
+        <v>241</v>
       </c>
       <c r="C550" t="s">
         <v>5</v>
@@ -8630,10 +8693,10 @@
     </row>
     <row r="551">
       <c r="A551" t="s">
+        <v>658</v>
+      </c>
+      <c r="B551" t="s">
         <v>659</v>
-      </c>
-      <c r="B551" t="s">
-        <v>233</v>
       </c>
       <c r="C551" t="s">
         <v>5</v>
@@ -8644,7 +8707,7 @@
         <v>660</v>
       </c>
       <c r="B552" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="C552" t="s">
         <v>5</v>
@@ -8655,7 +8718,7 @@
         <v>661</v>
       </c>
       <c r="B553" t="s">
-        <v>662</v>
+        <v>642</v>
       </c>
       <c r="C553" t="s">
         <v>5</v>
@@ -8663,10 +8726,10 @@
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B554" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="C554" t="s">
         <v>5</v>
@@ -8674,10 +8737,10 @@
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B555" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C555" t="s">
         <v>5</v>
@@ -8685,10 +8748,10 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B556" t="s">
-        <v>662</v>
+        <v>211</v>
       </c>
       <c r="C556" t="s">
         <v>5</v>
@@ -8696,10 +8759,10 @@
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B557" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C557" t="s">
         <v>5</v>
@@ -8707,10 +8770,10 @@
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B558" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="C558" t="s">
         <v>5</v>
@@ -8718,10 +8781,10 @@
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B559" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="C559" t="s">
         <v>5</v>
@@ -8729,10 +8792,10 @@
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B560" t="s">
-        <v>228</v>
+        <v>179</v>
       </c>
       <c r="C560" t="s">
         <v>5</v>
@@ -8740,10 +8803,10 @@
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B561" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="C561" t="s">
         <v>5</v>
@@ -8751,10 +8814,10 @@
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B562" t="s">
-        <v>135</v>
+        <v>498</v>
       </c>
       <c r="C562" t="s">
         <v>5</v>
@@ -8762,10 +8825,10 @@
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B563" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="C563" t="s">
         <v>5</v>
@@ -8773,10 +8836,10 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B564" t="s">
-        <v>379</v>
+        <v>249</v>
       </c>
       <c r="C564" t="s">
         <v>5</v>
@@ -8784,10 +8847,10 @@
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B565" t="s">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="C565" t="s">
         <v>5</v>
@@ -8795,10 +8858,10 @@
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B566" t="s">
-        <v>141</v>
+        <v>247</v>
       </c>
       <c r="C566" t="s">
         <v>5</v>
@@ -8806,10 +8869,10 @@
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B567" t="s">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="C567" t="s">
         <v>5</v>
@@ -8817,10 +8880,10 @@
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B568" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="C568" t="s">
         <v>5</v>
@@ -8828,10 +8891,10 @@
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B569" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="C569" t="s">
         <v>5</v>
@@ -8839,10 +8902,10 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B570" t="s">
-        <v>124</v>
+        <v>563</v>
       </c>
       <c r="C570" t="s">
         <v>5</v>
@@ -8850,10 +8913,10 @@
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B571" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="C571" t="s">
         <v>5</v>
@@ -8861,10 +8924,10 @@
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B572" t="s">
-        <v>124</v>
+        <v>256</v>
       </c>
       <c r="C572" t="s">
         <v>5</v>
@@ -8872,10 +8935,10 @@
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B573" t="s">
-        <v>108</v>
+        <v>259</v>
       </c>
       <c r="C573" t="s">
         <v>5</v>
@@ -8883,10 +8946,10 @@
     </row>
     <row r="574">
       <c r="A574" t="s">
+        <v>682</v>
+      </c>
+      <c r="B574" t="s">
         <v>683</v>
-      </c>
-      <c r="B574" t="s">
-        <v>374</v>
       </c>
       <c r="C574" t="s">
         <v>5</v>
@@ -8897,7 +8960,7 @@
         <v>684</v>
       </c>
       <c r="B575" t="s">
-        <v>395</v>
+        <v>256</v>
       </c>
       <c r="C575" t="s">
         <v>5</v>
@@ -8908,7 +8971,7 @@
         <v>685</v>
       </c>
       <c r="B576" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C576" t="s">
         <v>5</v>
@@ -8919,7 +8982,7 @@
         <v>686</v>
       </c>
       <c r="B577" t="s">
-        <v>252</v>
+        <v>683</v>
       </c>
       <c r="C577" t="s">
         <v>5</v>
@@ -8930,7 +8993,7 @@
         <v>687</v>
       </c>
       <c r="B578" t="s">
-        <v>99</v>
+        <v>206</v>
       </c>
       <c r="C578" t="s">
         <v>5</v>
@@ -8941,7 +9004,7 @@
         <v>688</v>
       </c>
       <c r="B579" t="s">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="C579" t="s">
         <v>5</v>
@@ -8952,7 +9015,7 @@
         <v>689</v>
       </c>
       <c r="B580" t="s">
-        <v>97</v>
+        <v>265</v>
       </c>
       <c r="C580" t="s">
         <v>5</v>
@@ -8963,7 +9026,7 @@
         <v>690</v>
       </c>
       <c r="B581" t="s">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="C581" t="s">
         <v>5</v>
@@ -8974,7 +9037,7 @@
         <v>691</v>
       </c>
       <c r="B582" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="C582" t="s">
         <v>5</v>
@@ -8985,7 +9048,7 @@
         <v>692</v>
       </c>
       <c r="B583" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="C583" t="s">
         <v>5</v>
@@ -8996,7 +9059,7 @@
         <v>693</v>
       </c>
       <c r="B584" t="s">
-        <v>252</v>
+        <v>158</v>
       </c>
       <c r="C584" t="s">
         <v>5</v>
@@ -9007,7 +9070,7 @@
         <v>694</v>
       </c>
       <c r="B585" t="s">
-        <v>247</v>
+        <v>400</v>
       </c>
       <c r="C585" t="s">
         <v>5</v>
@@ -9018,7 +9081,7 @@
         <v>695</v>
       </c>
       <c r="B586" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="C586" t="s">
         <v>5</v>
@@ -9029,7 +9092,7 @@
         <v>696</v>
       </c>
       <c r="B587" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="C587" t="s">
         <v>5</v>
@@ -9040,7 +9103,7 @@
         <v>697</v>
       </c>
       <c r="B588" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C588" t="s">
         <v>5</v>
@@ -9051,7 +9114,7 @@
         <v>698</v>
       </c>
       <c r="B589" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C589" t="s">
         <v>5</v>
@@ -9062,7 +9125,7 @@
         <v>699</v>
       </c>
       <c r="B590" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C590" t="s">
         <v>5</v>
@@ -9073,7 +9136,7 @@
         <v>700</v>
       </c>
       <c r="B591" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="C591" t="s">
         <v>5</v>
@@ -9084,7 +9147,7 @@
         <v>701</v>
       </c>
       <c r="B592" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="C592" t="s">
         <v>5</v>
@@ -9095,7 +9158,7 @@
         <v>702</v>
       </c>
       <c r="B593" t="s">
-        <v>159</v>
+        <v>17</v>
       </c>
       <c r="C593" t="s">
         <v>5</v>
@@ -9106,7 +9169,7 @@
         <v>703</v>
       </c>
       <c r="B594" t="s">
-        <v>477</v>
+        <v>25</v>
       </c>
       <c r="C594" t="s">
         <v>5</v>
@@ -9117,7 +9180,7 @@
         <v>704</v>
       </c>
       <c r="B595" t="s">
-        <v>479</v>
+        <v>395</v>
       </c>
       <c r="C595" t="s">
         <v>5</v>
@@ -9128,7 +9191,7 @@
         <v>705</v>
       </c>
       <c r="B596" t="s">
-        <v>228</v>
+        <v>416</v>
       </c>
       <c r="C596" t="s">
         <v>5</v>
@@ -9139,7 +9202,7 @@
         <v>706</v>
       </c>
       <c r="B597" t="s">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="C597" t="s">
         <v>5</v>
@@ -9150,7 +9213,7 @@
         <v>707</v>
       </c>
       <c r="B598" t="s">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="C598" t="s">
         <v>5</v>
@@ -9161,7 +9224,7 @@
         <v>708</v>
       </c>
       <c r="B599" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="C599" t="s">
         <v>5</v>
@@ -9172,7 +9235,7 @@
         <v>709</v>
       </c>
       <c r="B600" t="s">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="C600" t="s">
         <v>5</v>
@@ -9183,7 +9246,7 @@
         <v>710</v>
       </c>
       <c r="B601" t="s">
-        <v>285</v>
+        <v>124</v>
       </c>
       <c r="C601" t="s">
         <v>5</v>
@@ -9194,7 +9257,7 @@
         <v>711</v>
       </c>
       <c r="B602" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="C602" t="s">
         <v>5</v>
@@ -9205,7 +9268,7 @@
         <v>712</v>
       </c>
       <c r="B603" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="C603" t="s">
         <v>5</v>
@@ -9216,7 +9279,7 @@
         <v>713</v>
       </c>
       <c r="B604" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="C604" t="s">
         <v>5</v>
@@ -9227,7 +9290,7 @@
         <v>714</v>
       </c>
       <c r="B605" t="s">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="C605" t="s">
         <v>5</v>
@@ -9238,7 +9301,7 @@
         <v>715</v>
       </c>
       <c r="B606" t="s">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="C606" t="s">
         <v>5</v>
@@ -9249,7 +9312,7 @@
         <v>716</v>
       </c>
       <c r="B607" t="s">
-        <v>477</v>
+        <v>158</v>
       </c>
       <c r="C607" t="s">
         <v>5</v>
@@ -9260,7 +9323,7 @@
         <v>717</v>
       </c>
       <c r="B608" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C608" t="s">
         <v>5</v>
@@ -9271,7 +9334,7 @@
         <v>718</v>
       </c>
       <c r="B609" t="s">
-        <v>479</v>
+        <v>161</v>
       </c>
       <c r="C609" t="s">
         <v>5</v>
@@ -9282,7 +9345,7 @@
         <v>719</v>
       </c>
       <c r="B610" t="s">
-        <v>479</v>
+        <v>166</v>
       </c>
       <c r="C610" t="s">
         <v>5</v>
@@ -9293,7 +9356,7 @@
         <v>720</v>
       </c>
       <c r="B611" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="C611" t="s">
         <v>5</v>
@@ -9304,7 +9367,7 @@
         <v>721</v>
       </c>
       <c r="B612" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="C612" t="s">
         <v>5</v>
@@ -9315,7 +9378,7 @@
         <v>722</v>
       </c>
       <c r="B613" t="s">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="C613" t="s">
         <v>5</v>
@@ -9326,7 +9389,7 @@
         <v>723</v>
       </c>
       <c r="B614" t="s">
-        <v>580</v>
+        <v>182</v>
       </c>
       <c r="C614" t="s">
         <v>5</v>
@@ -9337,7 +9400,7 @@
         <v>724</v>
       </c>
       <c r="B615" t="s">
-        <v>580</v>
+        <v>498</v>
       </c>
       <c r="C615" t="s">
         <v>5</v>
@@ -9348,7 +9411,7 @@
         <v>725</v>
       </c>
       <c r="B616" t="s">
-        <v>585</v>
+        <v>500</v>
       </c>
       <c r="C616" t="s">
         <v>5</v>
@@ -9359,7 +9422,7 @@
         <v>726</v>
       </c>
       <c r="B617" t="s">
-        <v>587</v>
+        <v>251</v>
       </c>
       <c r="C617" t="s">
         <v>5</v>
@@ -9370,7 +9433,7 @@
         <v>727</v>
       </c>
       <c r="B618" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="C618" t="s">
         <v>5</v>
@@ -9381,7 +9444,7 @@
         <v>728</v>
       </c>
       <c r="B619" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C619" t="s">
         <v>5</v>
@@ -9392,7 +9455,7 @@
         <v>729</v>
       </c>
       <c r="B620" t="s">
-        <v>662</v>
+        <v>168</v>
       </c>
       <c r="C620" t="s">
         <v>5</v>
@@ -9403,7 +9466,7 @@
         <v>730</v>
       </c>
       <c r="B621" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="C621" t="s">
         <v>5</v>
@@ -9414,7 +9477,7 @@
         <v>731</v>
       </c>
       <c r="B622" t="s">
-        <v>188</v>
+        <v>308</v>
       </c>
       <c r="C622" t="s">
         <v>5</v>
@@ -9425,7 +9488,7 @@
         <v>732</v>
       </c>
       <c r="B623" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C623" t="s">
         <v>5</v>
@@ -9436,7 +9499,7 @@
         <v>733</v>
       </c>
       <c r="B624" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C624" t="s">
         <v>5</v>
@@ -9447,7 +9510,7 @@
         <v>734</v>
       </c>
       <c r="B625" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="C625" t="s">
         <v>5</v>
@@ -9458,7 +9521,7 @@
         <v>735</v>
       </c>
       <c r="B626" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="C626" t="s">
         <v>5</v>
@@ -9469,7 +9532,7 @@
         <v>736</v>
       </c>
       <c r="B627" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C627" t="s">
         <v>5</v>
@@ -9480,7 +9543,7 @@
         <v>737</v>
       </c>
       <c r="B628" t="s">
-        <v>220</v>
+        <v>498</v>
       </c>
       <c r="C628" t="s">
         <v>5</v>
@@ -9491,7 +9554,7 @@
         <v>738</v>
       </c>
       <c r="B629" t="s">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="C629" t="s">
         <v>5</v>
@@ -9502,7 +9565,7 @@
         <v>739</v>
       </c>
       <c r="B630" t="s">
-        <v>740</v>
+        <v>500</v>
       </c>
       <c r="C630" t="s">
         <v>5</v>
@@ -9510,10 +9573,10 @@
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B631" t="s">
-        <v>587</v>
+        <v>500</v>
       </c>
       <c r="C631" t="s">
         <v>5</v>
@@ -9521,10 +9584,10 @@
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B632" t="s">
-        <v>587</v>
+        <v>206</v>
       </c>
       <c r="C632" t="s">
         <v>5</v>
@@ -9532,10 +9595,10 @@
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B633" t="s">
-        <v>744</v>
+        <v>206</v>
       </c>
       <c r="C633" t="s">
         <v>5</v>
@@ -9543,12 +9606,243 @@
     </row>
     <row r="634">
       <c r="A634" t="s">
+        <v>743</v>
+      </c>
+      <c r="B634" t="s">
+        <v>254</v>
+      </c>
+      <c r="C634" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="s">
+        <v>744</v>
+      </c>
+      <c r="B635" t="s">
+        <v>601</v>
+      </c>
+      <c r="C635" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="s">
         <v>745</v>
       </c>
-      <c r="B634" t="s">
-        <v>585</v>
-      </c>
-      <c r="C634" t="s">
+      <c r="B636" t="s">
+        <v>601</v>
+      </c>
+      <c r="C636" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="s">
+        <v>746</v>
+      </c>
+      <c r="B637" t="s">
+        <v>606</v>
+      </c>
+      <c r="C637" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="s">
+        <v>747</v>
+      </c>
+      <c r="B638" t="s">
+        <v>608</v>
+      </c>
+      <c r="C638" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="s">
+        <v>748</v>
+      </c>
+      <c r="B639" t="s">
+        <v>206</v>
+      </c>
+      <c r="C639" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="s">
+        <v>749</v>
+      </c>
+      <c r="B640" t="s">
+        <v>206</v>
+      </c>
+      <c r="C640" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="s">
+        <v>750</v>
+      </c>
+      <c r="B641" t="s">
+        <v>683</v>
+      </c>
+      <c r="C641" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="s">
+        <v>751</v>
+      </c>
+      <c r="B642" t="s">
+        <v>211</v>
+      </c>
+      <c r="C642" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="s">
+        <v>752</v>
+      </c>
+      <c r="B643" t="s">
+        <v>211</v>
+      </c>
+      <c r="C643" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="s">
+        <v>753</v>
+      </c>
+      <c r="B644" t="s">
+        <v>243</v>
+      </c>
+      <c r="C644" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="s">
+        <v>754</v>
+      </c>
+      <c r="B645" t="s">
+        <v>243</v>
+      </c>
+      <c r="C645" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="s">
+        <v>755</v>
+      </c>
+      <c r="B646" t="s">
+        <v>206</v>
+      </c>
+      <c r="C646" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="s">
+        <v>756</v>
+      </c>
+      <c r="B647" t="s">
+        <v>202</v>
+      </c>
+      <c r="C647" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="s">
+        <v>757</v>
+      </c>
+      <c r="B648" t="s">
+        <v>206</v>
+      </c>
+      <c r="C648" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="s">
+        <v>758</v>
+      </c>
+      <c r="B649" t="s">
+        <v>243</v>
+      </c>
+      <c r="C649" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="s">
+        <v>759</v>
+      </c>
+      <c r="B650" t="s">
+        <v>243</v>
+      </c>
+      <c r="C650" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="s">
+        <v>760</v>
+      </c>
+      <c r="B651" t="s">
+        <v>761</v>
+      </c>
+      <c r="C651" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="s">
+        <v>762</v>
+      </c>
+      <c r="B652" t="s">
+        <v>608</v>
+      </c>
+      <c r="C652" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="s">
+        <v>763</v>
+      </c>
+      <c r="B653" t="s">
+        <v>608</v>
+      </c>
+      <c r="C653" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="s">
+        <v>764</v>
+      </c>
+      <c r="B654" t="s">
+        <v>765</v>
+      </c>
+      <c r="C654" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="s">
+        <v>766</v>
+      </c>
+      <c r="B655" t="s">
+        <v>606</v>
+      </c>
+      <c r="C655" t="s">
         <v>5</v>
       </c>
     </row>
